--- a/artfynd/A 60385-2025 artfynd.xlsx
+++ b/artfynd/A 60385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132435843</v>
+        <v>132435602</v>
       </c>
       <c r="B2" t="n">
-        <v>79332</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sankt Olofsleden, Sankt Olofsleden, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448315</v>
+        <v>448161</v>
       </c>
       <c r="R2" t="n">
-        <v>7029420</v>
+        <v>7029365</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,11 +753,6 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran med full längd.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,12 +779,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Liggande död trädstam, utan markontakt</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -802,32 +802,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132435805</v>
+        <v>132435640</v>
       </c>
       <c r="B3" t="n">
-        <v>79332</v>
+        <v>96410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>448335</v>
+        <v>448367</v>
       </c>
       <c r="R3" t="n">
-        <v>7029415</v>
+        <v>7029432</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -887,26 +887,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -924,50 +904,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132436240</v>
+        <v>132435824</v>
       </c>
       <c r="B4" t="n">
-        <v>57957</v>
+        <v>96410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2812</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sankt Olofsleden, Sankt Olofsleden, Jmt</t>
+          <t>Hökån, Hökån, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448147</v>
+        <v>448318</v>
       </c>
       <c r="R4" t="n">
-        <v>7029360</v>
+        <v>7029413</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -1002,11 +977,6 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på en gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1019,26 +989,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,53 +1006,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132435602</v>
+        <v>132435758</v>
       </c>
       <c r="B5" t="n">
-        <v>91917</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sankt Olofsleden, Sankt Olofsleden, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448161</v>
+        <v>448337</v>
       </c>
       <c r="R5" t="n">
-        <v>7029365</v>
+        <v>7029473</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1160,12 +1105,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1183,53 +1128,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132436089</v>
+        <v>132435805</v>
       </c>
       <c r="B6" t="n">
-        <v>57957</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sankt Olofsleden, Sankt Olofsleden, Jmt</t>
+          <t>Hökån, Hökån, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448157</v>
+        <v>448335</v>
       </c>
       <c r="R6" t="n">
-        <v>7029370</v>
+        <v>7029415</v>
       </c>
       <c r="S6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,11 +1201,6 @@
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, längs några meter på en gran.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1292,12 +1227,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1315,14 +1250,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132435879</v>
+        <v>132435843</v>
       </c>
       <c r="B7" t="n">
-        <v>79332</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1350,13 +1285,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448270</v>
+        <v>448315</v>
       </c>
       <c r="R7" t="n">
-        <v>7029441</v>
+        <v>7029420</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1390,7 +1325,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På grenar av en stående död gran med full längd.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1419,12 +1354,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1442,14 +1377,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132435758</v>
+        <v>132435879</v>
       </c>
       <c r="B8" t="n">
-        <v>79332</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1477,13 +1412,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448337</v>
+        <v>448270</v>
       </c>
       <c r="R8" t="n">
-        <v>7029473</v>
+        <v>7029441</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,6 +1448,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1561,6 +1501,402 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132436025</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sankt Olofsleden, Sankt Olofsleden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>448141</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7029371</v>
+      </c>
+      <c r="S9" t="n">
+        <v>4</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs flera meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132436089</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sankt Olofsleden, Sankt Olofsleden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>448157</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7029370</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, längs några meter på en gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132436240</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sankt Olofsleden, Sankt Olofsleden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>448147</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7029360</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, enstaka på en gran.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60385-2025 artfynd.xlsx
+++ b/artfynd/A 60385-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132435602</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132435640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132435824</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132435758</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,6 +1272,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132435805</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1374,6 +1404,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132435843</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1501,6 +1536,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132435879</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1633,6 +1673,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132436025</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1765,6 +1810,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132436089</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1897,8 +1947,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132436240</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>